--- a/artfynd/A 14671-2026 artfynd.xlsx
+++ b/artfynd/A 14671-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,63 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120970077</v>
+        <v>120745508</v>
       </c>
       <c r="B2" t="n">
-        <v>56563</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>N om Ockelbo, Gstr</t>
+          <t>Stortjärnsbäcken, Stortjärnsbäcken, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589307</v>
+        <v>589537</v>
       </c>
       <c r="R2" t="n">
-        <v>6764943</v>
+        <v>6764827</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,22 +743,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,81 +767,67 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marta Lomas Vega</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marta Lomas Vega, Elin Lönnberg</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120970098</v>
+        <v>121640373</v>
       </c>
       <c r="B3" t="n">
-        <v>56563</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>N om Ockelbo, Gstr</t>
+          <t>Ockelbo- Grönviken, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589305</v>
+        <v>589536</v>
       </c>
       <c r="R3" t="n">
-        <v>6764713</v>
+        <v>6764829</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,22 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>08:40</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>08:40</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,75 +871,64 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marta Lomas Vega</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marta Lomas Vega, Elin Lönnberg</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>JMN0138 NVI Ockelbo-Grönviken</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120970096</v>
+        <v>121640375</v>
       </c>
       <c r="B4" t="n">
-        <v>56563</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>N om Ockelbo, Gstr</t>
+          <t>Ockelbo- Grönviken, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589310</v>
+        <v>589391</v>
       </c>
       <c r="R4" t="n">
-        <v>6764780</v>
+        <v>6764989</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,22 +952,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>08:40</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>08:40</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>En fruktkropp.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,75 +977,64 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marta Lomas Vega</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marta Lomas Vega, Elin Lönnberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>JMN0138 NVI Ockelbo-Grönviken</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120970084</v>
+        <v>121640376</v>
       </c>
       <c r="B5" t="n">
-        <v>56563</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>N om Ockelbo, Gstr</t>
+          <t>Ockelbo- Grönviken, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589267</v>
+        <v>589371</v>
       </c>
       <c r="R5" t="n">
-        <v>6764942</v>
+        <v>6765037</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1121,22 +1058,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:21</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:21</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rester av en fruktkropp.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,27 +1083,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marta Lomas Vega</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marta Lomas Vega, Elin Lönnberg</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>JMN0138 NVI Ockelbo-Grönviken</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>120970068</v>
       </c>
       <c r="B6" t="n">
-        <v>56563</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1285,15 +1216,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120970078</v>
+        <v>120970069</v>
       </c>
       <c r="B7" t="n">
-        <v>56563</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589297</v>
+        <v>589333</v>
       </c>
       <c r="R7" t="n">
-        <v>6764941</v>
+        <v>6765083</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,7 +1296,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1380,7 +1306,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1407,15 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120970069</v>
+        <v>120970077</v>
       </c>
       <c r="B8" t="n">
-        <v>56563</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589333</v>
+        <v>589307</v>
       </c>
       <c r="R8" t="n">
-        <v>6765083</v>
+        <v>6764943</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1492,7 +1413,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1502,7 +1423,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1529,53 +1450,58 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121640376</v>
+        <v>120970078</v>
       </c>
       <c r="B9" t="n">
-        <v>92056</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ockelbo- Grönviken, Gstr</t>
+          <t>N om Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589371</v>
+        <v>589297</v>
       </c>
       <c r="R9" t="n">
-        <v>6765037</v>
+        <v>6764941</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1599,17 +1525,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rester av en fruktkropp.</t>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,69 +1555,70 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Marta Lomas Vega</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>JMN0138 NVI Ockelbo-Grönviken</t>
-        </is>
-      </c>
+          <t>Marta Lomas Vega, Elin Lönnberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121640373</v>
+        <v>120970084</v>
       </c>
       <c r="B10" t="n">
-        <v>80589</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1049</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ockelbo- Grönviken, Gstr</t>
+          <t>N om Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589536</v>
+        <v>589267</v>
       </c>
       <c r="R10" t="n">
-        <v>6764829</v>
+        <v>6764942</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1710,12 +1642,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,69 +1672,70 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Marta Lomas Vega</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>JMN0138 NVI Ockelbo-Grönviken</t>
-        </is>
-      </c>
+          <t>Marta Lomas Vega, Elin Lönnberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121640375</v>
+        <v>120970096</v>
       </c>
       <c r="B11" t="n">
-        <v>92056</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ockelbo- Grönviken, Gstr</t>
+          <t>N om Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589391</v>
+        <v>589310</v>
       </c>
       <c r="R11" t="n">
-        <v>6764989</v>
+        <v>6764780</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1816,17 +1759,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>En fruktkropp.</t>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1841,19 +1789,690 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
+          <t>Marta Lomas Vega</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Marta Lomas Vega, Elin Lönnberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120970098</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>N om Ockelbo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>589305</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6764713</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marta Lomas Vega</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Marta Lomas Vega, Elin Lönnberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121640374</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ockelbo- Grönviken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>589396</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6764983</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre spillning.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Mika Thunell</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
+      <c r="AY13" t="inlineStr">
         <is>
           <t>JMN0138 NVI Ockelbo-Grönviken</t>
         </is>
       </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>116631264</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lisstjärnsberget, Gstr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>589500</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6764699</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>06:56</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>06:56</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Arvid Löf</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Arvid Löf</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>116631265</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58463</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102995</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Buskskvätta</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Saxicola rubetra</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lisstjärnsberget, Gstr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>589500</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6764699</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>06:56</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>06:56</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Arvid Löf</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Arvid Löf</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>119302572</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mellan Stortjärnen och Lisstjärnen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>589531</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6764880</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>fuktigt äldre gallringsbestånd med tall</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>119302573</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mellan Stortjärnen och Lisstjärnen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>589549</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6764791</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>fuktigt äldre gallringsbestånd med tall</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
